--- a/src/nodes/HPC/compressor_stage_8_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_8_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.00082096999836998364</v>
       </c>
       <c r="B2">
-        <v>0.00081971155701380909</v>
+        <v>0.00077111013311030618</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0016419399967399673</v>
       </c>
       <c r="B3">
-        <v>0.0011815444806500784</v>
+        <v>0.0011145533287830877</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0024629099951099511</v>
       </c>
       <c r="B4">
-        <v>0.0014756320736563323</v>
+        <v>0.0013944545602175083</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0032838799934799346</v>
       </c>
       <c r="B5">
-        <v>0.0017236558288781876</v>
+        <v>0.0016310504130620533</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.004104849991849918</v>
       </c>
       <c r="B6">
-        <v>0.0019344530301847545</v>
+        <v>0.0018325895149724997</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0049258199902199023</v>
       </c>
       <c r="B7">
-        <v>0.0021130662632926961</v>
+        <v>0.0020037787371096844</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0057467899885898857</v>
       </c>
       <c r="B8">
-        <v>0.0022624588033676829</v>
+        <v>0.0021473842416110749</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0065677599869598691</v>
       </c>
       <c r="B9">
-        <v>0.002387265743392957</v>
+        <v>0.0022677325116302873</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0073887299853298526</v>
       </c>
       <c r="B10">
-        <v>0.0024924918449529547</v>
+        <v>0.002369495033712006</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.008209699983699836</v>
       </c>
       <c r="B11">
-        <v>0.002582948726219305</v>
+        <v>0.00245716298694905</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.0090306699820698211</v>
       </c>
       <c r="B12">
-        <v>0.0026612036702946718</v>
+        <v>0.0025331328177946632</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.0098516399804398046</v>
       </c>
       <c r="B13">
-        <v>0.0027210397634186622</v>
+        <v>0.0025916023495956573</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.010672609978809788</v>
       </c>
       <c r="B14">
-        <v>0.0027587379357791909</v>
+        <v>0.0026291007062589013</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.011493579977179771</v>
       </c>
       <c r="B15">
-        <v>0.0027893546902204589</v>
+        <v>0.0026596808370379231</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.012314549975549753</v>
       </c>
       <c r="B16">
-        <v>0.0028266997773771377</v>
+        <v>0.0026962320379411947</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.013135519973919738</v>
       </c>
       <c r="B17">
-        <v>0.0028608203663895056</v>
+        <v>0.0027294651666503081</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.013956489972289723</v>
       </c>
       <c r="B18">
-        <v>0.0028788645537771731</v>
+        <v>0.0027473852562480703</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.014777459970659705</v>
       </c>
       <c r="B19">
-        <v>0.0028801467270714756</v>
+        <v>0.0027493524797490274</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.01559842996902969</v>
       </c>
       <c r="B20">
-        <v>0.0028670228465566823</v>
+        <v>0.0027375657951506623</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.016419399967399672</v>
       </c>
       <c r="B21">
-        <v>0.0028418488725170605</v>
+        <v>0.0027142241604504566</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.017240369965769657</v>
       </c>
       <c r="B22">
-        <v>0.0028065613982873536</v>
+        <v>0.0026811351043020933</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.018061339964139642</v>
       </c>
       <c r="B23">
-        <v>0.0027614195494042077</v>
+        <v>0.0026385404379840652</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.018882309962509624</v>
       </c>
       <c r="B24">
-        <v>0.0027062630844547453</v>
+        <v>0.0025862905434310647</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.019703279960879609</v>
       </c>
       <c r="B25">
-        <v>0.0026409317620260885</v>
+        <v>0.002524235802577786</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.020524249959249591</v>
       </c>
       <c r="B26">
-        <v>0.0025651962102155442</v>
+        <v>0.002452162056092287</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.021345219957619576</v>
       </c>
       <c r="B27">
-        <v>0.0024785505351611532</v>
+        <v>0.0023695969795760807</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.022166189955989558</v>
       </c>
       <c r="B28">
-        <v>0.0023804197125111416</v>
+        <v>0.0022760037073640458</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.022987159954359543</v>
       </c>
       <c r="B29">
-        <v>0.0022702287179137363</v>
+        <v>0.00217084537379106</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.023808129952729528</v>
       </c>
       <c r="B30">
-        <v>0.0021477148972001065</v>
+        <v>0.0020538766389464479</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.024629099951099506</v>
       </c>
       <c r="B31">
-        <v>0.002013865076933193</v>
+        <v>0.0019260182659373169</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.025450069949469491</v>
       </c>
       <c r="B32">
-        <v>0.0018699784538588795</v>
+        <v>0.0017884825436252192</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.026271039947839477</v>
       </c>
       <c r="B33">
-        <v>0.0017173542247230502</v>
+        <v>0.0016424817608717075</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.027092009946209462</v>
       </c>
       <c r="B34">
-        <v>0.0015567867483185676</v>
+        <v>0.0014887570037262123</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.027912979944579447</v>
       </c>
       <c r="B35">
-        <v>0.0013870510316262069</v>
+        <v>0.001326164546989669</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.028733949942949425</v>
       </c>
       <c r="B36">
-        <v>0.0012064172436737236</v>
+        <v>0.0011530894626508911</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.02955491994131941</v>
       </c>
       <c r="B37">
-        <v>0.0010131555534888693</v>
+        <v>0.00096791682269868964</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.030375889939689395</v>
       </c>
       <c r="B38">
-        <v>0.00080429811211532338</v>
+        <v>0.00076787619683231663</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.031196859938059381</v>
       </c>
       <c r="B39">
-        <v>0.00057192499866046251</v>
+        <v>0.00054557514559277966</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.032017829936429362</v>
       </c>
       <c r="B40">
-        <v>0.00030687827424758733</v>
+        <v>0.00029246572723152478</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.032017829936429362</v>
       </c>
       <c r="B43">
-        <v>-0.00012549813623428691</v>
+        <v>-0.00011108558921822435</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.031196859938059381</v>
       </c>
       <c r="B44">
-        <v>-0.00021857059337002571</v>
+        <v>-0.00019222074030234268</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.030375889939689395</v>
       </c>
       <c r="B45">
-        <v>-0.00028835934637488095</v>
+        <v>-0.00025193743109187415</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.02955491994131941</v>
       </c>
       <c r="B46">
-        <v>-0.000344006370216518</v>
+        <v>-0.00029876763942633845</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.028733949942949425</v>
       </c>
       <c r="B47">
-        <v>-0.00039341618701124319</v>
+        <v>-0.000340088405988411</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.027912979944579447</v>
       </c>
       <c r="B48">
-        <v>-0.0004395435074699276</v>
+        <v>-0.00037865702283338976</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.027092009946209462</v>
       </c>
       <c r="B49">
-        <v>-0.00048410558945208412</v>
+        <v>-0.00041607584485972896</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.026271039947839477</v>
       </c>
       <c r="B50">
-        <v>-0.000528819690817225</v>
+        <v>-0.00045394722696588235</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.025450069949469491</v>
       </c>
       <c r="B51">
-        <v>-0.00057489885315093576</v>
+        <v>-0.00049340294291727517</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.024629099951099506</v>
       </c>
       <c r="B52">
-        <v>-0.000621539252943095</v>
+        <v>-0.00053369244194721873</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.023808129952729528</v>
       </c>
       <c r="B53">
-        <v>-0.00066743285040965386</v>
+        <v>-0.00057359459215599532</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.022987159954359543</v>
       </c>
       <c r="B54">
-        <v>-0.0007112716057665646</v>
+        <v>-0.00061188826164388808</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.022166189955989558</v>
       </c>
       <c r="B55">
-        <v>-0.00075206044190175112</v>
+        <v>-0.00064764443675465475</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.021345219957619576</v>
       </c>
       <c r="B56">
-        <v>-0.00079005613239102775</v>
+        <v>-0.00068110257680595494</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.020524249959249591</v>
       </c>
       <c r="B57">
-        <v>-0.00082582841348218124</v>
+        <v>-0.00071279425935892376</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.019703279960879609</v>
       </c>
       <c r="B58">
-        <v>-0.0008599470214229988</v>
+        <v>-0.00074325106197469578</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.018882309962509624</v>
       </c>
       <c r="B59">
-        <v>-0.00089291314625568015</v>
+        <v>-0.00077294060523199913</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.018061339964139642</v>
       </c>
       <c r="B60">
-        <v>-0.00092495379320007578</v>
+        <v>-0.00080207468177993281</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.017240369965769657</v>
       </c>
       <c r="B61">
-        <v>-0.00095622742127044922</v>
+        <v>-0.00083080112728518894</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.016419399967399672</v>
       </c>
       <c r="B62">
-        <v>-0.00098689248948106382</v>
+        <v>-0.00085926777741445956</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.01559842996902969</v>
       </c>
       <c r="B63">
-        <v>-0.0010166886956239209</v>
+        <v>-0.00088723164421790053</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.014777459970659705</v>
       </c>
       <c r="B64">
-        <v>-0.001043680692601972</v>
+        <v>-0.00091288644527952345</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.013956489972289723</v>
       </c>
       <c r="B65">
-        <v>-0.0010655143720959069</v>
+        <v>-0.00093403507456680406</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.013135519973919738</v>
       </c>
       <c r="B66">
-        <v>-0.0010798356257864154</v>
+        <v>-0.00094848042604721782</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.012314549975549753</v>
       </c>
       <c r="B67">
-        <v>-0.0010873324057011492</v>
+        <v>-0.0009568646662652064</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.011493579977179771</v>
       </c>
       <c r="B68">
-        <v>-0.0011008609052556109</v>
+        <v>-0.00097118705207307511</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.010672609978809788</v>
       </c>
       <c r="B69">
-        <v>-0.0011303789498295035</v>
+        <v>-0.0010007417203092136</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.0098516399804398046</v>
       </c>
       <c r="B70">
-        <v>-0.0011620826512714901</v>
+        <v>-0.0010326452374484849</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.0090306699820698211</v>
       </c>
       <c r="B71">
-        <v>-0.0011809219047055977</v>
+        <v>-0.0010528510522055886</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.008209699983699836</v>
       </c>
       <c r="B72">
-        <v>-0.0011906234518883566</v>
+        <v>-0.0010648377126181009</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0073887299853298526</v>
       </c>
       <c r="B73">
-        <v>-0.0011974124922755074</v>
+        <v>-0.0010744156810345584</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0065677599869598691</v>
       </c>
       <c r="B74">
-        <v>-0.0011987312094871316</v>
+        <v>-0.0010791979777244618</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0057467899885898857</v>
       </c>
       <c r="B75">
-        <v>-0.0011897780493305467</v>
+        <v>-0.0010747034875739389</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0049258199902199023</v>
       </c>
       <c r="B76">
-        <v>-0.0011655595221976701</v>
+        <v>-0.0010562719960146578</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.004104849991849918</v>
       </c>
       <c r="B77">
-        <v>-0.0011214524261828854</v>
+        <v>-0.0010195889109706306</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0032838799934799346</v>
       </c>
       <c r="B78">
-        <v>-0.0010545066456058364</v>
+        <v>-0.00096190122978970206</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0024629099951099511</v>
       </c>
       <c r="B79">
-        <v>-0.000959693329508387</v>
+        <v>-0.0008785158160695628</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0016419399967399673</v>
       </c>
       <c r="B80">
-        <v>-0.00082819007535964075</v>
+        <v>-0.00076119892349265012</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.00082096999836998364</v>
       </c>
       <c r="B81">
-        <v>-0.00063833116009128161</v>
+        <v>-0.00058972973618777859</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.00095000022659441239</v>
       </c>
       <c r="B2">
-        <v>0.00041152838373664189</v>
+        <v>0.00031451436059682058</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0019000004531888248</v>
       </c>
       <c r="B3">
-        <v>0.00060146698270091092</v>
+        <v>0.00046774495080548152</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0028500006797832372</v>
       </c>
       <c r="B4">
-        <v>0.00075791764110241507</v>
+        <v>0.00059587800245265959</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0038000009063776496</v>
       </c>
       <c r="B5">
-        <v>0.00089133206190892557</v>
+        <v>0.00070648101781818488</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0047500011329720615</v>
       </c>
       <c r="B6">
-        <v>0.0010059691909990506</v>
+        <v>0.00080263791738192209</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0057000013595664744</v>
       </c>
       <c r="B7">
-        <v>0.0011042585035221223</v>
+        <v>0.00088610805148879438</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0066500015861608872</v>
       </c>
       <c r="B8">
-        <v>0.0011876270058893334</v>
+        <v>0.00095792496631070113</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0076000018127552992</v>
       </c>
       <c r="B9">
-        <v>0.0012583079481235024</v>
+        <v>0.0010197058912120498</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.00855000203934971</v>
       </c>
       <c r="B10">
-        <v>0.0013187129004027345</v>
+        <v>0.00107319714112076</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0095000022659441231</v>
       </c>
       <c r="B11">
-        <v>0.0013711604699146551</v>
+        <v>0.0011200776900262956</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.010450002492538536</v>
       </c>
       <c r="B12">
-        <v>0.0014168872299686276</v>
+        <v>0.0011612431016681604</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.011400002719132949</v>
       </c>
       <c r="B13">
-        <v>0.0014528945813514457</v>
+        <v>0.0011945226397244726</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.01235000294572736</v>
       </c>
       <c r="B14">
-        <v>0.0014773883501924524</v>
+        <v>0.0012186175534883408</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.013300003172321774</v>
       </c>
       <c r="B15">
-        <v>0.0014976272365137598</v>
+        <v>0.0012387833347742147</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.014250003398916186</v>
       </c>
       <c r="B16">
-        <v>0.0015202688854982756</v>
+        <v>0.0012598402956328979</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.015200003625510598</v>
       </c>
       <c r="B17">
-        <v>0.0015405138490793208</v>
+        <v>0.0012783137865392631</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.016150003852105011</v>
       </c>
       <c r="B18">
-        <v>0.0015521649745427223</v>
+        <v>0.0012897171985635403</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.01710000407869942</v>
       </c>
       <c r="B19">
-        <v>0.0015548913838339122</v>
+        <v>0.0012938110467333166</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.018050004305293837</v>
       </c>
       <c r="B20">
-        <v>0.0015498287675632244</v>
+        <v>0.0012914176270655184</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.019000004531888246</v>
       </c>
       <c r="B21">
-        <v>0.0015381128163409928</v>
+        <v>0.0012833592355770726</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.019950004758482659</v>
       </c>
       <c r="B22">
-        <v>0.0015206771012408022</v>
+        <v>0.0012703118154173345</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.020900004985077072</v>
       </c>
       <c r="B23">
-        <v>0.0014976467151892429</v>
+        <v>0.0012523658982653751</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.021850005211671485</v>
       </c>
       <c r="B24">
-        <v>0.0014689446315761566</v>
+        <v>0.0012294656629326958</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.022800005438265897</v>
       </c>
       <c r="B25">
-        <v>0.0014344938237913841</v>
+        <v>0.0012015552882307969</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.023750005664860307</v>
       </c>
       <c r="B26">
-        <v>0.0013941840107056171</v>
+        <v>0.0011685548590684889</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.02470000589145472</v>
       </c>
       <c r="B27">
-        <v>0.0013477718931129451</v>
+        <v>0.0011302880847438204</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.025650006118049132</v>
       </c>
       <c r="B28">
-        <v>0.0012949809172883074</v>
+        <v>0.00108655458065215</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.026600006344643549</v>
       </c>
       <c r="B29">
-        <v>0.0012355345295066438</v>
+        <v>0.0010371539621888361</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.027550006571237962</v>
       </c>
       <c r="B30">
-        <v>0.0011693068648987197</v>
+        <v>0.00098199492573216337</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.028500006797832371</v>
       </c>
       <c r="B31">
-        <v>0.0010967748140186067</v>
+        <v>0.0009214224915921192</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.029450007024426784</v>
       </c>
       <c r="B32">
-        <v>0.0010185659562762016</v>
+        <v>0.00085589076106161661</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.030400007251021197</v>
       </c>
       <c r="B33">
-        <v>0.00093530787108140213</v>
+        <v>0.0007858538354335691</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.031350007477615606</v>
       </c>
       <c r="B34">
-        <v>0.0008473848118475863</v>
+        <v>0.00071158962960801459</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.032300007704210022</v>
       </c>
       <c r="B35">
-        <v>0.000754207728002056</v>
+        <v>0.00063267131291349071</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.033250007930804432</v>
       </c>
       <c r="B36">
-        <v>0.0006549442429755935</v>
+        <v>0.00054849586828566014</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.034200008157398841</v>
       </c>
       <c r="B37">
-        <v>0.00054876198019898062</v>
+        <v>0.00045846027866018471</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.035150008383993257</v>
       </c>
       <c r="B38">
-        <v>0.0004342317252872706</v>
+        <v>0.00036152939995874123</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.036100008610587674</v>
       </c>
       <c r="B39">
-        <v>0.00030753691259259927</v>
+        <v>0.0002549395800470638</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.037050008837182083</v>
       </c>
       <c r="B40">
-        <v>0.0001642641386513733</v>
+        <v>0.00013549503977690043</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.038000009063776492</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>3.2959753905132266E-20</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.038000009063776492</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-4.1199692381415332E-21</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.037050008837182083</v>
       </c>
       <c r="B43">
-        <v>-4.4207592323067946E-05</v>
+        <v>-1.5438493448595055E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.036100008610587674</v>
       </c>
       <c r="B44">
-        <v>-7.3603178317078273E-05</v>
+        <v>-2.100584577154278E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.035150008383993257</v>
       </c>
       <c r="B45">
-        <v>-9.259671912236206E-05</v>
+        <v>-1.9894393793832774E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.034200008157398841</v>
       </c>
       <c r="B46">
-        <v>-0.00010559817587925059</v>
+        <v>-1.5296474340454716E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.033250007930804432</v>
       </c>
       <c r="B47">
-        <v>-0.00011642079100943067</v>
+        <v>-9.9724163194973515E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.032300007704210022</v>
       </c>
       <c r="B48">
-        <v>-0.00012649093206001084</v>
+        <v>-4.954516971445649E-06</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.031350007477615606</v>
       </c>
       <c r="B49">
-        <v>-0.00013663824785945531</v>
+        <v>-8.4306561988356816E-07</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.030400007251021197</v>
       </c>
       <c r="B50">
-        <v>-0.0001476923872362281</v>
+        <v>1.7616484116048626E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.029450007024426784</v>
       </c>
       <c r="B51">
-        <v>-0.00016023980614832668</v>
+        <v>2.4353890662582154E-06</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.028500006797832371</v>
       </c>
       <c r="B52">
-        <v>-0.00017389418907188208</v>
+        <v>1.4581333546053682E-06</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.027550006571237962</v>
       </c>
       <c r="B53">
-        <v>-0.00018802602761255855</v>
+        <v>-7.1408844600220936E-07</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.026600006344643549</v>
       </c>
       <c r="B54">
-        <v>-0.00020200581337602073</v>
+        <v>-3.6252460582130839E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.025650006118049132</v>
       </c>
       <c r="B55">
-        <v>-0.0002153548554374728</v>
+        <v>-6.9285188013151637E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.02470000589145472</v>
       </c>
       <c r="B56">
-        <v>-0.00022819773275027869</v>
+        <v>-1.0713924381153838E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.023750005664860307</v>
       </c>
       <c r="B57">
-        <v>-0.00024080984173734232</v>
+        <v>-1.5180690100213894E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.022800005438265897</v>
       </c>
       <c r="B58">
-        <v>-0.00025346657882156738</v>
+        <v>-2.0528043260980072E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.021850005211671485</v>
       </c>
       <c r="B59">
-        <v>-0.00026641021366631274</v>
+        <v>-2.6931245022851987E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.020900004985077072</v>
       </c>
       <c r="B60">
-        <v>-0.00027975050889675627</v>
+        <v>-3.4469691972888404E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.019950004758482659</v>
       </c>
       <c r="B61">
-        <v>-0.0002935641003785308</v>
+        <v>-4.31988145550629E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.019000004531888246</v>
       </c>
       <c r="B62">
-        <v>-0.0003079276239772691</v>
+        <v>-5.3174043213349046E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.018050004305293837</v>
       </c>
       <c r="B63">
-        <v>-0.00032271572879696321</v>
+        <v>-6.4304588299257345E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.01710000407869942</v>
       </c>
       <c r="B64">
-        <v>-0.00033699511689504175</v>
+        <v>-7.5914779794446143E-05</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.016150003852105011</v>
       </c>
       <c r="B65">
-        <v>-0.00034963050356729271</v>
+        <v>-8.718272758811063E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.015200003625510598</v>
       </c>
       <c r="B66">
-        <v>-0.00035948660410950391</v>
+        <v>-9.72865415694461E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.014250003398916186</v>
       </c>
       <c r="B67">
-        <v>-0.00036689480917837447</v>
+        <v>-0.00010646621931299681</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.013300003172321774</v>
       </c>
       <c r="B68">
-        <v>-0.00037805321087424823</v>
+        <v>-0.00011920930913470319</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.01235000294572736</v>
       </c>
       <c r="B69">
-        <v>-0.00039776235056198007</v>
+        <v>-0.00013899155385786835</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.011400002719132949</v>
       </c>
       <c r="B70">
-        <v>-0.00041936586522082223</v>
+        <v>-0.00016099392359384928</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.010450002492538536</v>
       </c>
       <c r="B71">
-        <v>-0.00043560645336809177</v>
+        <v>-0.00017996232506762449</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0095000022659441231</v>
       </c>
       <c r="B72">
-        <v>-0.00044827996405896346</v>
+        <v>-0.00019719718417060414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.00855000203934971</v>
       </c>
       <c r="B73">
-        <v>-0.00046038680453910897</v>
+        <v>-0.00021487104525713457</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0076000018127552992</v>
       </c>
       <c r="B74">
-        <v>-0.00047069246427832833</v>
+        <v>-0.00023209040736687573</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0066500015861608872</v>
       </c>
       <c r="B75">
-        <v>-0.00047688052728916161</v>
+        <v>-0.00024717848771052938</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0057000013595664744</v>
       </c>
       <c r="B76">
-        <v>-0.00047654187353097979</v>
+        <v>-0.00025839142149765174</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0047500011329720615</v>
       </c>
       <c r="B77">
-        <v>-0.00046744583521202528</v>
+        <v>-0.00026411456159489681</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0038000009063776496</v>
       </c>
       <c r="B78">
-        <v>-0.00044816825758919562</v>
+        <v>-0.00026331721349845486</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0028500006797832372</v>
       </c>
       <c r="B79">
-        <v>-0.00041628263896827859</v>
+        <v>-0.0002542430003185229</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0019000004531888248</v>
       </c>
       <c r="B80">
-        <v>-0.00036753324842538944</v>
+        <v>-0.00023381121652996003</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00095000022659441239</v>
       </c>
       <c r="B81">
-        <v>-0.00029147178394322318</v>
+        <v>-0.00019445776080340184</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0010672609978809788</v>
       </c>
       <c r="B2">
-        <v>0.00028160915749494552</v>
+        <v>0.00020263184365175308</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0021345219957619576</v>
       </c>
       <c r="B3">
-        <v>0.00041364144707868431</v>
+        <v>0.00030478082529482455</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0032017829936429368</v>
       </c>
       <c r="B4">
-        <v>0.00052288806208502527</v>
+        <v>0.00039097460274693628</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0042690439915239152</v>
       </c>
       <c r="B5">
-        <v>0.00061639347993735127</v>
+        <v>0.00046590967923613319</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.005336304989404894</v>
       </c>
       <c r="B6">
-        <v>0.00069702792441979431</v>
+        <v>0.0005314997121998804</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0064035659872858737</v>
       </c>
       <c r="B7">
-        <v>0.00076642848959637634</v>
+        <v>0.00058883625954898151</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0074708269851668525</v>
       </c>
       <c r="B8">
-        <v>0.00082555656731788144</v>
+        <v>0.00063856040446339381</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.00853808798304783</v>
       </c>
       <c r="B9">
-        <v>0.0008759170525712459</v>
+        <v>0.00068167555095690756</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.00960534898092881</v>
       </c>
       <c r="B10">
-        <v>0.000919135061757308</v>
+        <v>0.000719265243490766</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.010672609978809788</v>
       </c>
       <c r="B11">
-        <v>0.00095677309379635714</v>
+        <v>0.000752371267482192</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.011739870976690768</v>
       </c>
       <c r="B12">
-        <v>0.00098966431483251088</v>
+        <v>0.0007815491795199964</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.012807131974571747</v>
       </c>
       <c r="B13">
-        <v>0.0010157871773857458</v>
+        <v>0.00080545137992336252</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.013874392972452725</v>
       </c>
       <c r="B14">
-        <v>0.0010339320112993575</v>
+        <v>0.00082327151332888644</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.014941653970333705</v>
       </c>
       <c r="B15">
-        <v>0.0010489913693340588</v>
+        <v>0.00083827135791243832</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.016008914968214681</v>
       </c>
       <c r="B16">
-        <v>0.00106545267777281</v>
+        <v>0.00085344260118940289</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.017076175966095661</v>
       </c>
       <c r="B17">
-        <v>0.0010800806340701419</v>
+        <v>0.000866628434493946</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.01814343696397664</v>
       </c>
       <c r="B18">
-        <v>0.0010886978263760362</v>
+        <v>0.0008750439678912443</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.01921069796185762</v>
       </c>
       <c r="B19">
-        <v>0.0010910811344507119</v>
+        <v>0.00087854048255173341</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.0202779589597386</v>
       </c>
       <c r="B20">
-        <v>0.0010879960109569467</v>
+        <v>0.0008776283024221639</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.021345219957619576</v>
       </c>
       <c r="B21">
-        <v>0.0010802079085575184</v>
+        <v>0.0008728177514492866</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.022412480955500556</v>
       </c>
       <c r="B22">
-        <v>0.0010683460623291626</v>
+        <v>0.00086452833460311479</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.023479741953381535</v>
       </c>
       <c r="B23">
-        <v>0.0010524948370044464</v>
+        <v>0.00085281628094671419</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.024547002951262515</v>
       </c>
       <c r="B24">
-        <v>0.0010326023797298941</v>
+        <v>0.00083764700056641276</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.025614263949143495</v>
       </c>
       <c r="B25">
-        <v>0.0010086168376520312</v>
+        <v>0.00081898590354853888</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.026681524947024471</v>
       </c>
       <c r="B26">
-        <v>0.00098046396453236174</v>
+        <v>0.00079678346408206826</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.027748785944905451</v>
       </c>
       <c r="B27">
-        <v>0.00094797994059230679</v>
+        <v>0.00077093041276656362</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.02881604694278643</v>
       </c>
       <c r="B28">
-        <v>0.0009109785526682676</v>
+        <v>0.000741302544304236</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.02988330794066741</v>
       </c>
       <c r="B29">
-        <v>0.00086927358759664489</v>
+        <v>0.00070777565339729526</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.03095056893854839</v>
       </c>
       <c r="B30">
-        <v>0.00082278042778323316</v>
+        <v>0.00067029325812103776</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.032017829936429362</v>
       </c>
       <c r="B31">
-        <v>0.00077182083791140128</v>
+        <v>0.00062906977004310242</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.033085090934310342</v>
       </c>
       <c r="B32">
-        <v>0.00071681817823391139</v>
+        <v>0.0005843873241042131</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.034152351932191322</v>
       </c>
       <c r="B33">
-        <v>0.00065819580900352615</v>
+        <v>0.00053652805524509462</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.0352196129300723</v>
       </c>
       <c r="B34">
-        <v>0.00059621309748593822</v>
+        <v>0.00048566476252336126</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.036286873927953281</v>
       </c>
       <c r="B35">
-        <v>0.000530473438998562</v>
+        <v>0.0004315329014641879</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.037354134925834261</v>
       </c>
       <c r="B36">
-        <v>0.00046041623587174212</v>
+        <v>0.0003737585917096397</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.03842139592371524</v>
       </c>
       <c r="B37">
-        <v>0.00038548089043582279</v>
+        <v>0.00031196795290178088</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.03948865692159622</v>
       </c>
       <c r="B38">
-        <v>0.00030470452170539811</v>
+        <v>0.00024551890937051196</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.0405559179194772</v>
       </c>
       <c r="B39">
-        <v>0.00021551511543205912</v>
+        <v>0.0001726966041970743</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.041623178917358179</v>
       </c>
       <c r="B40">
-        <v>0.00011493837405164611</v>
+        <v>9.1517985150544581E-05</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.042690439915239152</v>
       </c>
       <c r="B42">
-        <v>4.6285067700464182E-21</v>
+        <v>5.7856334625580228E-22</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.041623178917358179</v>
       </c>
       <c r="B43">
-        <v>-2.558395935496302E-05</v>
+        <v>-2.1635704538614848E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.0405559179194772</v>
       </c>
       <c r="B44">
-        <v>-4.1395951977849631E-05</v>
+        <v>1.422559257135181E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.03948865692159622</v>
       </c>
       <c r="B45">
-        <v>-5.0409152303918417E-05</v>
+        <v>8.7764600309676858E-06</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.03842139592371524</v>
       </c>
       <c r="B46">
-        <v>-5.559673476842815E-05</v>
+        <v>1.7916202765613689E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.037354134925834261</v>
       </c>
       <c r="B47">
-        <v>-5.9529629100872137E-05</v>
+        <v>2.712801506123026E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.036286873927953281</v>
       </c>
       <c r="B48">
-        <v>-6.3169786207681916E-05</v>
+        <v>3.5770751326692089E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.0352196129300723</v>
       </c>
       <c r="B49">
-        <v>-6.7076912289523621E-05</v>
+        <v>4.3471422673053388E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.034152351932191322</v>
       </c>
       <c r="B50">
-        <v>-7.181071354706336E-05</v>
+        <v>4.9857040211368259E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.033085090934310342</v>
       </c>
       <c r="B51">
-        <v>-7.7766946544278627E-05</v>
+        <v>5.466390758541975E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.032017829936429362</v>
       </c>
       <c r="B52">
-        <v>-8.4685569298392411E-05</v>
+        <v>5.8065498569906572E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.03095056893854839</v>
       </c>
       <c r="B53">
-        <v>-9.2142590189939075E-05</v>
+        <v>6.0344579472256329E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.02988330794066741</v>
       </c>
       <c r="B54">
-        <v>-9.9714017599453038E-05</v>
+        <v>6.1783916599896652E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.02881604694278643</v>
       </c>
       <c r="B55">
-        <v>-0.00010707749751592263</v>
+        <v>6.2598510848109148E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.027748785944905451</v>
       </c>
       <c r="B56">
-        <v>-0.00011431722636215196</v>
+        <v>6.2732301463591241E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.026681524947024471</v>
       </c>
       <c r="B57">
-        <v>-0.00012161903816939916</v>
+        <v>6.2061462280894392E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.025614263949143495</v>
       </c>
       <c r="B58">
-        <v>-0.00012916876696892233</v>
+        <v>6.0462167134570017E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.024547002951262515</v>
       </c>
       <c r="B59">
-        <v>-0.00013712989525099424</v>
+        <v>5.782548391248726E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.023479741953381535</v>
       </c>
       <c r="B60">
-        <v>-0.000145576499341946</v>
+        <v>5.4102056715786145E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.022412480955500556</v>
       </c>
       <c r="B61">
-        <v>-0.00015456030402712337</v>
+        <v>4.9257423698924388E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.021345219957619576</v>
       </c>
       <c r="B62">
-        <v>-0.00016413303409187213</v>
+        <v>4.3257123016359729E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.0202779589597386</v>
       </c>
       <c r="B63">
-        <v>-0.00017421024025174949</v>
+        <v>3.6157468283033294E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.01921069796185762</v>
       </c>
       <c r="B64">
-        <v>-0.00018416277694315885</v>
+        <v>2.8377874955819686E-05</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.01814343696397664</v>
       </c>
       <c r="B65">
-        <v>-0.00019322532453271496</v>
+        <v>2.0428533952076959E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.017076175966095661</v>
       </c>
       <c r="B66">
-        <v>-0.0002006325633870327</v>
+        <v>1.2819636189163086E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.016008914968214681</v>
       </c>
       <c r="B67">
-        <v>-0.00020660778172763335</v>
+        <v>5.4022948557739209E-06</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.014941653970333705</v>
       </c>
       <c r="B68">
-        <v>-0.00021532869919566389</v>
+        <v>-4.6086877740434057E-06</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.013874392972452725</v>
       </c>
       <c r="B69">
-        <v>-0.0002300309765234685</v>
+        <v>-1.9370478552997457E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.012807131974571747</v>
       </c>
       <c r="B70">
-        <v>-0.0002462276073885538</v>
+        <v>-3.5891809926170448E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.011739870976690768</v>
       </c>
       <c r="B71">
-        <v>-0.00025902649704257678</v>
+        <v>-5.0911361730062117E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.010672609978809788</v>
       </c>
       <c r="B72">
-        <v>-0.00026963786408863309</v>
+        <v>-6.5236037774467985E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.00960534898092881</v>
       </c>
       <c r="B73">
-        <v>-0.00028008384784194241</v>
+        <v>-8.0214029575400629E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.00853808798304783</v>
       </c>
       <c r="B74">
-        <v>-0.00028953195711478304</v>
+        <v>-9.5290455500444835E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0074708269851668525</v>
       </c>
       <c r="B75">
-        <v>-0.00029642040980904324</v>
+        <v>-0.0001094242469545557</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0064035659872858737</v>
       </c>
       <c r="B76">
-        <v>-0.00029912489068799277</v>
+        <v>-0.0001215326606405978</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.005336304989404894</v>
       </c>
       <c r="B77">
-        <v>-0.00029614134889968885</v>
+        <v>-0.00013061313667977494</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0042690439915239152</v>
       </c>
       <c r="B78">
-        <v>-0.00028650932426995665</v>
+        <v>-0.00013602552356873862</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0032017829936429368</v>
       </c>
       <c r="B79">
-        <v>-0.00026859269394350851</v>
+        <v>-0.00013667923460541955</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0021345219957619576</v>
       </c>
       <c r="B80">
-        <v>-0.00023952228362447451</v>
+        <v>-0.00013066166184061469</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0010672609978809788</v>
       </c>
       <c r="B81">
-        <v>-0.00019225472556420902</v>
+        <v>-0.00011327741172101658</v>
       </c>
     </row>
     <row r="82" spans="1:2">
